--- a/测试集/边缘情况/双行表头.xlsx
+++ b/测试集/边缘情况/双行表头.xlsx
@@ -465,49 +465,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DD203</t>
+          <t>DD342</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>硒鼓</t>
+          <t>签字笔(盒)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>388</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>388</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DD507</t>
+          <t>DD577</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>签字笔(盒)</t>
+          <t>订书机</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DD715</t>
+          <t>DD914</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -516,139 +516,139 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DD628</t>
+          <t>DD193</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>激光打印机</t>
+          <t>碎纸机</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1299</v>
+        <v>599</v>
       </c>
       <c r="E6" t="n">
-        <v>3897</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DD340</t>
+          <t>DD574</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>签字笔(盒)</t>
+          <t>A4打印纸(箱)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>89.5</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>268.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DD103</t>
+          <t>DD552</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>激光打印机</t>
+          <t>碎纸机</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1299</v>
+        <v>599</v>
       </c>
       <c r="E8" t="n">
-        <v>2598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DD880</t>
+          <t>DD559</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>签字笔(盒)</t>
+          <t>会议记录本</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DD254</t>
+          <t>DD865</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>激光打印机</t>
+          <t>会议记录本</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1299</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>3897</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DD523</t>
+          <t>DD517</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>会议记录本</t>
+          <t>签字笔(盒)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
